--- a/results/undisturbed_results.xlsx
+++ b/results/undisturbed_results.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/goksuuzunturk/Desktop/Tez/TS-Anomaly-Detection/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFBFCCA-79A0-BB48-9DE2-54E700F8B93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27390C7-6BD7-2E47-8319-C360842BC801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17040" xr2:uid="{5695BB89-A94E-8845-9E46-FE92494F803C}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16920" activeTab="1" xr2:uid="{5695BB89-A94E-8845-9E46-FE92494F803C}"/>
   </bookViews>
   <sheets>
     <sheet name="Confusion Matrix" sheetId="1" r:id="rId1"/>
+    <sheet name="Normal Class Recall" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="19">
   <si>
     <t>Model Name</t>
   </si>
@@ -90,6 +91,9 @@
   </si>
   <si>
     <t>Recall for Normal Class</t>
+  </si>
+  <si>
+    <t>Recall</t>
   </si>
 </sst>
 </file>
@@ -165,7 +169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -173,6 +177,10 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1083,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="4">
-        <f t="shared" ref="J29:J31" si="2">B29/(B29+C29+D29+E29+F29+G29+H29+I29)</f>
+        <f>B29/(B29+C29+D29+E29+F29+G29+H29+I29)</f>
         <v>0.82512303941861009</v>
       </c>
     </row>
@@ -1123,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="4">
-        <f t="shared" si="2"/>
+        <f>B30/(B30+C30+D30+E30+F30+G30+H30+I30)</f>
         <v>0.77967894761050571</v>
       </c>
     </row>
@@ -1163,8 +1171,238 @@
         <v>0</v>
       </c>
       <c r="J31" s="4">
-        <f t="shared" si="2"/>
+        <f>B31/(B31+C31+D31+E31+F31+G31+H31+I31)</f>
         <v>0.77597449696249199</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA575E4-478B-F242-8B93-45746D6A87B6}">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="34" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <f>'Confusion Matrix'!B4 / ('Confusion Matrix'!B4 + 'Confusion Matrix'!C4 + 'Confusion Matrix'!D4 + 'Confusion Matrix'!E4 + 'Confusion Matrix'!F4 + 'Confusion Matrix'!G4 + 'Confusion Matrix'!H4 + 'Confusion Matrix'!I4)</f>
+        <v>0.91947861714661772</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5">
+        <f>'Confusion Matrix'!B5 / ('Confusion Matrix'!B5 + 'Confusion Matrix'!C5 + 'Confusion Matrix'!D5 + 'Confusion Matrix'!E5 + 'Confusion Matrix'!F5 + 'Confusion Matrix'!G5 + 'Confusion Matrix'!H5 + 'Confusion Matrix'!I5)</f>
+        <v>0.95970746515799643</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5">
+        <f>'Confusion Matrix'!B6 / ('Confusion Matrix'!B6 + 'Confusion Matrix'!C6 + 'Confusion Matrix'!D6 + 'Confusion Matrix'!E6 + 'Confusion Matrix'!F6 + 'Confusion Matrix'!G6 + 'Confusion Matrix'!H6 + 'Confusion Matrix'!I6)</f>
+        <v>0.93485898674252477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5">
+        <f>'Confusion Matrix'!B7 / ('Confusion Matrix'!B7 + 'Confusion Matrix'!C7 + 'Confusion Matrix'!D7 + 'Confusion Matrix'!E7 + 'Confusion Matrix'!F7 + 'Confusion Matrix'!G7 + 'Confusion Matrix'!H7 + 'Confusion Matrix'!I7)</f>
+        <v>0.96935601999766485</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:2" ht="34" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5">
+        <f>'Confusion Matrix'!B12 / ('Confusion Matrix'!B12 + 'Confusion Matrix'!C12 + 'Confusion Matrix'!D12 + 'Confusion Matrix'!E12 + 'Confusion Matrix'!F12 + 'Confusion Matrix'!G12 + 'Confusion Matrix'!H12 + 'Confusion Matrix'!I12)</f>
+        <v>0.58031440065385143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="5">
+        <f>'Confusion Matrix'!B13 / ('Confusion Matrix'!B13 + 'Confusion Matrix'!C13 + 'Confusion Matrix'!D13 + 'Confusion Matrix'!E13 + 'Confusion Matrix'!F13 + 'Confusion Matrix'!G13 + 'Confusion Matrix'!H13 + 'Confusion Matrix'!I13)</f>
+        <v>0.72639076116377066</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5">
+        <f>'Confusion Matrix'!B14 / ('Confusion Matrix'!B14 + 'Confusion Matrix'!C14 + 'Confusion Matrix'!D14 + 'Confusion Matrix'!E14 + 'Confusion Matrix'!F14 + 'Confusion Matrix'!G14 + 'Confusion Matrix'!H14 + 'Confusion Matrix'!I14)</f>
+        <v>0.60930252305993993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="5">
+        <f>'Confusion Matrix'!B15 / ('Confusion Matrix'!B15 + 'Confusion Matrix'!C15 + 'Confusion Matrix'!D15 + 'Confusion Matrix'!E15 + 'Confusion Matrix'!F15 + 'Confusion Matrix'!G15 + 'Confusion Matrix'!H15 + 'Confusion Matrix'!I15)</f>
+        <v>0.61018352421691735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2" ht="34" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5">
+        <f>'Confusion Matrix'!B20 / ('Confusion Matrix'!B20 + 'Confusion Matrix'!C20 + 'Confusion Matrix'!D20 + 'Confusion Matrix'!E20 + 'Confusion Matrix'!F20 + 'Confusion Matrix'!G20 + 'Confusion Matrix'!H20 + 'Confusion Matrix'!I20)</f>
+        <v>0.77874133593741712</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="5">
+        <f>'Confusion Matrix'!B21 / ('Confusion Matrix'!B21 + 'Confusion Matrix'!C21 + 'Confusion Matrix'!D21 + 'Confusion Matrix'!E21 + 'Confusion Matrix'!F21 + 'Confusion Matrix'!G21 + 'Confusion Matrix'!H21 + 'Confusion Matrix'!I21)</f>
+        <v>0.78927089193406286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5">
+        <f>'Confusion Matrix'!B22 / ('Confusion Matrix'!B22 + 'Confusion Matrix'!C22 + 'Confusion Matrix'!D22 + 'Confusion Matrix'!E22 + 'Confusion Matrix'!F22 + 'Confusion Matrix'!G22 + 'Confusion Matrix'!H22 + 'Confusion Matrix'!I22)</f>
+        <v>0.79487533302905178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="5">
+        <f>'Confusion Matrix'!B23 / ('Confusion Matrix'!B23 + 'Confusion Matrix'!C23 + 'Confusion Matrix'!D23 + 'Confusion Matrix'!E23 + 'Confusion Matrix'!F23 + 'Confusion Matrix'!G23 + 'Confusion Matrix'!H23 + 'Confusion Matrix'!I23)</f>
+        <v>0.74838394667289387</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:2" ht="34" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="5">
+        <f>(B4+B12+B20)/3</f>
+        <v>0.75951145124596209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="5">
+        <f t="shared" ref="B29:B31" si="0">(B5+B13+B21)/3</f>
+        <v>0.82512303941860987</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5">
+        <f t="shared" si="0"/>
+        <v>0.77967894761050538</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7759744969624921</v>
       </c>
     </row>
   </sheetData>
